--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T20:31:09+00:00</t>
+    <t>2026-09-14T10:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:59:28+00:00</t>
+    <t>2026-09-14T11:54:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:54:38+00:00</t>
+    <t>2026-09-14T13:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$219</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6303" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7105" uniqueCount="869">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:10:06+00:00</t>
+    <t>2026-09-14T14:30:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2515,9 +2515,7 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
     &lt;code value="103392008"/&gt;
-    &lt;display value="Semi-quantitative value"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -2544,10 +2542,195 @@
     <t>Zaehlung je Gesichtsfeld, UCUM-Einheit /[HPF]. Fuer offene Grenzen wird Quantity.comparator verwendet, z. B. '&lt;10/GF' als comparator = '&lt;', value = 10.</t>
   </si>
   <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.value</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].value</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].comparator</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].unit</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.system</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].code</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-mikroskopie-gesichtsfeld-einheiten-ucum</t>
+  </si>
+  <si>
     <t>Observation.component:menge.value[x]:valueRange</t>
   </si>
   <si>
     <t>Zaehlung je Gesichtsfeld als Intervall, UCUM-Einheit /[HPF] — z. B. '10-25/GF' als low = 10, high = 25.</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.id</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+</t>
+  </si>
+  <si>
+    <t>Low limit</t>
+  </si>
+  <si>
+    <t>The low limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Range.low</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.id</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.value</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.value</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.comparator</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.comparator</t>
+  </si>
+  <si>
+    <t>Not allowed to be used in this context</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.unit</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.unit</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.system</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.system</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.low.code</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].low.code</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high</t>
+  </si>
+  <si>
+    <t>High limit</t>
+  </si>
+  <si>
+    <t>The high limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the high element is missing, the high boundary is not known.</t>
+  </si>
+  <si>
+    <t>Range.high</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.id</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.value</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.value</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.comparator</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.comparator</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.unit</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.unit</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.system</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.system</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange.high.code</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].high.code</t>
   </si>
   <si>
     <t>Observation.component:menge.dataAbsentReason</t>
@@ -2877,11 +3060,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ194"/>
+  <dimension ref="A1:AJ219"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.3828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="33.6953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2905,7 +3088,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="101.1796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="104.390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -22404,11 +22587,9 @@
         <v>803</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
         <v>77</v>
       </c>
@@ -22426,23 +22607,19 @@
         <v>77</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>626</v>
+        <v>99</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>804</v>
+        <v>100</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N191" s="2"/>
+      <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>77</v>
       </c>
@@ -22490,7 +22667,7 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>769</v>
+        <v>102</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>75</v>
@@ -22499,10 +22676,10 @@
         <v>84</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" hidden="true">
@@ -22510,18 +22687,18 @@
         <v>805</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>77</v>
@@ -22533,20 +22710,18 @@
         <v>77</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>287</v>
+        <v>105</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>774</v>
+        <v>106</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>775</v>
+        <v>107</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>634</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>77</v>
       </c>
@@ -22570,62 +22745,62 @@
         <v>77</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>777</v>
+        <v>77</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>778</v>
+        <v>77</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>773</v>
+        <v>112</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>636</v>
+        <v>77</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>779</v>
+        <v>808</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>638</v>
+        <v>77</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>77</v>
@@ -22634,22 +22809,22 @@
         <v>77</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>287</v>
+        <v>573</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>780</v>
+        <v>574</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>781</v>
+        <v>575</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>641</v>
+        <v>576</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>642</v>
+        <v>577</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
@@ -22674,13 +22849,13 @@
         <v>77</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>782</v>
+        <v>77</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>783</v>
+        <v>77</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>77</v>
@@ -22698,16 +22873,16 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>779</v>
+        <v>578</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>92</v>
@@ -22715,10 +22890,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>784</v>
+        <v>810</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22729,96 +22904,2658 @@
         <v>75</v>
       </c>
       <c r="G194" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N194" s="2"/>
+      <c r="O194" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q194" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="R194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="195" hidden="true">
+      <c r="A195" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="C195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G195" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J195" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K195" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N195" s="2"/>
+      <c r="O195" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q195" s="2"/>
+      <c r="R195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF195" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI195" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ195" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="196" hidden="true">
+      <c r="A196" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="C196" s="2"/>
+      <c r="D196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E196" s="2"/>
+      <c r="F196" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G196" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J196" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K196" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L196" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M196" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N196" s="2"/>
+      <c r="O196" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="P196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q196" s="2"/>
+      <c r="R196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE196" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF196" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG196" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH196" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI196" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AJ196" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="197" hidden="true">
+      <c r="A197" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C197" s="2"/>
+      <c r="D197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E197" s="2"/>
+      <c r="F197" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J197" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K197" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L197" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M197" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N197" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="P197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q197" s="2"/>
+      <c r="R197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X197" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y197" s="2"/>
+      <c r="Z197" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AA197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF197" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG197" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ197" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="198" hidden="true">
+      <c r="A198" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E198" s="2"/>
+      <c r="F198" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G198" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J198" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K198" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L198" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="M198" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O198" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q198" s="2"/>
+      <c r="R198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE198" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF198" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG198" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH198" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI198" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ198" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="199" hidden="true">
+      <c r="A199" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C199" s="2"/>
+      <c r="D199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E199" s="2"/>
+      <c r="F199" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K199" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L199" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M199" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N199" s="2"/>
+      <c r="O199" s="2"/>
+      <c r="P199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q199" s="2"/>
+      <c r="R199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF199" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG199" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI199" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ199" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="200" hidden="true">
+      <c r="A200" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C200" s="2"/>
+      <c r="D200" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E200" s="2"/>
+      <c r="F200" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G200" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="H194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K194" t="s" s="2">
+      <c r="H200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K200" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L200" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M200" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N200" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O200" s="2"/>
+      <c r="P200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q200" s="2"/>
+      <c r="R200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB200" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC200" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE200" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AF200" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG200" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH200" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI200" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ200" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="201" hidden="true">
+      <c r="A201" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="C201" s="2"/>
+      <c r="D201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E201" s="2"/>
+      <c r="F201" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J201" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K201" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="L201" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="M201" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="N201" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="O201" s="2"/>
+      <c r="P201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q201" s="2"/>
+      <c r="R201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF201" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="AG201" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI201" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ201" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="202" hidden="true">
+      <c r="A202" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="C202" s="2"/>
+      <c r="D202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E202" s="2"/>
+      <c r="F202" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K202" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L202" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M202" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N202" s="2"/>
+      <c r="O202" s="2"/>
+      <c r="P202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q202" s="2"/>
+      <c r="R202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF202" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG202" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ202" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="203" hidden="true">
+      <c r="A203" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="C203" s="2"/>
+      <c r="D203" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E203" s="2"/>
+      <c r="F203" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G203" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K203" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L203" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M203" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O203" s="2"/>
+      <c r="P203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q203" s="2"/>
+      <c r="R203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB203" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC203" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE203" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AF203" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG203" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH203" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI203" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ203" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="204" hidden="true">
+      <c r="A204" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="C204" s="2"/>
+      <c r="D204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J204" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K204" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L204" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M204" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N204" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O204" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="P204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q204" s="2"/>
+      <c r="R204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF204" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG204" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI204" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ204" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="205" hidden="true">
+      <c r="A205" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="C205" s="2"/>
+      <c r="D205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E205" s="2"/>
+      <c r="F205" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G205" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I205" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J205" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K205" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L205" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M205" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="N205" s="2"/>
+      <c r="O205" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q205" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="R205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X205" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y205" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z205" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF205" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG205" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH205" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI205" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ205" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="206" hidden="true">
+      <c r="A206" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="C206" s="2"/>
+      <c r="D206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E206" s="2"/>
+      <c r="F206" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G206" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J206" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K206" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L206" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M206" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N206" s="2"/>
+      <c r="O206" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q206" s="2"/>
+      <c r="R206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF206" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG206" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH206" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI206" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ206" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="207" hidden="true">
+      <c r="A207" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="C207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E207" s="2"/>
+      <c r="F207" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G207" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J207" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K207" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L207" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M207" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N207" s="2"/>
+      <c r="O207" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="P207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q207" s="2"/>
+      <c r="R207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE207" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF207" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG207" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH207" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI207" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AJ207" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="208" hidden="true">
+      <c r="A208" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="C208" s="2"/>
+      <c r="D208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E208" s="2"/>
+      <c r="F208" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J208" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K208" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L208" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M208" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="P208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q208" s="2"/>
+      <c r="R208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X208" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y208" s="2"/>
+      <c r="Z208" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AA208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF208" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG208" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI208" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ208" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="209" hidden="true">
+      <c r="A209" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="C209" s="2"/>
+      <c r="D209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E209" s="2"/>
+      <c r="F209" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G209" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J209" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K209" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="L209" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="M209" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="O209" s="2"/>
+      <c r="P209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q209" s="2"/>
+      <c r="R209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF209" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="AG209" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH209" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI209" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ209" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="210" hidden="true">
+      <c r="A210" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="C210" s="2"/>
+      <c r="D210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E210" s="2"/>
+      <c r="F210" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K210" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L210" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M210" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N210" s="2"/>
+      <c r="O210" s="2"/>
+      <c r="P210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q210" s="2"/>
+      <c r="R210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF210" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG210" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI210" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ210" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="211" hidden="true">
+      <c r="A211" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="C211" s="2"/>
+      <c r="D211" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E211" s="2"/>
+      <c r="F211" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G211" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K211" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L211" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M211" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O211" s="2"/>
+      <c r="P211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q211" s="2"/>
+      <c r="R211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB211" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC211" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE211" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AF211" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG211" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH211" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI211" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ211" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="212" hidden="true">
+      <c r="A212" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="C212" s="2"/>
+      <c r="D212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E212" s="2"/>
+      <c r="F212" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G212" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J212" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K212" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L212" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M212" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="P212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q212" s="2"/>
+      <c r="R212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF212" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG212" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH212" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI212" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ212" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="213" hidden="true">
+      <c r="A213" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E213" s="2"/>
+      <c r="F213" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G213" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I213" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J213" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K213" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L213" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M213" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="N213" s="2"/>
+      <c r="O213" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q213" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="R213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X213" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y213" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z213" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF213" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG213" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH213" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI213" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ213" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="214" hidden="true">
+      <c r="A214" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="C214" s="2"/>
+      <c r="D214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E214" s="2"/>
+      <c r="F214" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G214" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J214" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K214" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L214" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M214" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q214" s="2"/>
+      <c r="R214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF214" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG214" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH214" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI214" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ214" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="215" hidden="true">
+      <c r="A215" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="C215" s="2"/>
+      <c r="D215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E215" s="2"/>
+      <c r="F215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G215" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J215" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K215" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L215" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M215" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N215" s="2"/>
+      <c r="O215" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="P215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q215" s="2"/>
+      <c r="R215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE215" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF215" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH215" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI215" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AJ215" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="216" hidden="true">
+      <c r="A216" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C216" s="2"/>
+      <c r="D216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E216" s="2"/>
+      <c r="F216" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G216" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J216" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K216" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L216" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M216" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N216" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="P216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q216" s="2"/>
+      <c r="R216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X216" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y216" s="2"/>
+      <c r="Z216" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AA216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF216" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG216" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH216" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI216" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ216" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="217" hidden="true">
+      <c r="A217" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C217" s="2"/>
+      <c r="D217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G217" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K217" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L217" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="M217" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="P217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q217" s="2"/>
+      <c r="R217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X217" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y217" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="Z217" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AA217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF217" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AG217" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH217" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI217" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AJ217" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="N218" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O218" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="219" hidden="true">
+      <c r="A219" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K219" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="L194" t="s" s="2">
+      <c r="L219" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="M219" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="N219" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="O194" t="s" s="2">
+      <c r="O219" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="P194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF194" t="s" s="2">
+      <c r="P219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q219" s="2"/>
+      <c r="R219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF219" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="AG194" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH194" t="s" s="2">
+      <c r="AG219" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH219" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AI194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
+      <c r="AI219" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ219" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ194">
+  <autoFilter ref="A1:AJ219">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22828,7 +25565,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI193">
+  <conditionalFormatting sqref="A2:AI218">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:30:50+00:00</t>
+    <t>2026-09-14T14:45:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:45:51+00:00</t>
+    <t>2026-09-14T16:08:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:08:05+00:00</t>
+    <t>2026-09-14T16:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:39:15+00:00</t>
+    <t>2026-09-14T18:28:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
